--- a/output/pdf_financials_xlsx/EW.xlsx
+++ b/output/pdf_financials_xlsx/EW.xlsx
@@ -6051,34 +6051,34 @@
         <v>3.180335</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.838213</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.320538</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.487746</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.047193</v>
+        <v>-0.282325</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.591975</v>
+        <v>0.473572</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.181568</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.535399</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.480808</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.176006</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-0.66625</v>
       </c>
       <c r="Q91" s="3" t="n">
         <v>0</v>
@@ -11463,7 +11463,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EW.xlsx
+++ b/output/pdf_financials_xlsx/EW.xlsx
@@ -1127,37 +1127,37 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.114456</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.06751500000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.075392</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.049811</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.07416399999999999</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.067023</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.014511</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011565</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.140951</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.286182</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.2586</v>
       </c>
     </row>
     <row r="13">
@@ -2207,37 +2207,37 @@
         <v>-7.858379</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.584435</v>
+        <v>-6.698891</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.871656</v>
+        <v>-3.939171</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-6.30497</v>
+        <v>-6.380362</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.786543</v>
+        <v>-0.836354</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.341453</v>
+        <v>-1.415617</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.89079</v>
+        <v>0.823767</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.584572</v>
+        <v>-0.599083</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.04059</v>
+        <v>-2.052155</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.874133</v>
+        <v>0.733182</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.13123</v>
+        <v>0.845048</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.13123</v>
+        <v>0.87263</v>
       </c>
     </row>
     <row r="28">
@@ -2331,37 +2331,37 @@
         <v>-6.452122</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.766698</v>
+        <v>-3.881154</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.871656</v>
+        <v>-3.939171</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-6.30497</v>
+        <v>-6.380362</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.160718</v>
+        <v>0.110907</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.78533</v>
+        <v>-0.859494</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.310299</v>
+        <v>1.243276</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.27029</v>
+        <v>-0.284801</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.871066</v>
+        <v>-1.882631</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.023755</v>
+        <v>0.882804</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.13123</v>
+        <v>0.845048</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.13123</v>
+        <v>0.87263</v>
       </c>
     </row>
     <row r="30">
@@ -2616,55 +2616,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.714192</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.714192</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>25.60114</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>21.208781</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>12.27381</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>8.401122000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>7.694932</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.912735</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.030573</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.657694</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.908264</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.434218</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.145788</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>5.004988</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>6.400011</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.162445</v>
       </c>
     </row>
     <row r="35">
@@ -2732,55 +2732,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.714192</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.714192</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>25.60114</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>21.208781</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>12.27381</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>8.401122000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>7.694932</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.912735</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.030573</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.657694</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.908264</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.434218</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.145788</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>5.004988</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>6.400011</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.162445</v>
       </c>
     </row>
     <row r="37">
@@ -3428,52 +3428,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002066</v>
+        <v>0.001313</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.714192</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.714192</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.632365</v>
+        <v>0.031225</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>21.227609</v>
+        <v>0.018828</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.336535</v>
+        <v>0.062725</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>8.690071</v>
+        <v>0.288949</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.03232</v>
+        <v>0.337388</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.990107</v>
+        <v>0.077372</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.089358</v>
+        <v>0.058785</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.690955</v>
+        <v>0.033261</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.931005</v>
+        <v>0.022741</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.50937</v>
+        <v>0.075152</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.450947</v>
+        <v>0.305159</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.288634</v>
+        <v>0.283646</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.381939</v>
+        <v>0.981928</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -32933,7 +32933,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
